--- a/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_cosine_weighted_dose_att.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_cosine_weighted_dose_att.xlsx
@@ -488,10 +488,10 @@
         <v>-0.0550621776188822</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.0416240102898222</v>
+        <v>0.028856197423345</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>-0.0499276895180693</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.0390715925357221</v>
+        <v>0.0265286007151561</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>-0.046296636151758</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.0372716836407373</v>
+        <v>0.0247429087735578</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>-0.0430473784107456</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.0356648618570914</v>
+        <v>0.0242213038841599</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>-0.038681813376476</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.0335120524566912</v>
+        <v>0.0224945312065896</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>-0.0342813968874987</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.0301256963108134</v>
+        <v>0.0215262720881413</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>-0.0326096461499349</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.0287928554181065</v>
+        <v>0.0202811734856176</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>-0.0305281003277854</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.0271370147172937</v>
+        <v>0.0207428985638734</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>-0.027887055147231</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.0250423141350136</v>
+        <v>0.0206037996492567</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>-0.0256570200928916</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.0232792947166427</v>
+        <v>0.0204645408108431</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>-0.0227105542427615</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.0209583661153044</v>
+        <v>0.020267252256948</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>-0.0197276844025495</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.0186192573598528</v>
+        <v>0.019845514429616</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>-0.00920844842436341</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.0104673842978358</v>
+        <v>0.0217579782679584</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>-0.00450518887917402</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.00912913379157371</v>
+        <v>0.0222908311842118</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>-0.000562868005816416</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.00974067847612826</v>
+        <v>0.0223655158724718</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>0.00587405643895512</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.0108367127762411</v>
+        <v>0.0217431692849319</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>0.0111225981130744</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.00969679407526259</v>
+        <v>0.0228517377421345</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>0.0134029661309273</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.00865956009318942</v>
+        <v>0.0248536291122523</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>0.0169195703471694</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.0070761183751158</v>
+        <v>0.0250947594169263</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>0.0194492455636667</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.00801491150275193</v>
+        <v>0.025518369231057</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>0.0216806581646847</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.00883823159002374</v>
+        <v>0.025160555476979</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>0.0231069043847488</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.00935364108543713</v>
+        <v>0.0256962955028149</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>0.0278215690228483</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.0109848553044799</v>
+        <v>0.0295952304929682</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>0.0305454435798804</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.0118636419911456</v>
+        <v>0.0295613042657529</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>0.0330717776685357</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.0126230580663248</v>
+        <v>0.0300380849170049</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>0.0336250836070989</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.0128085340357417</v>
+        <v>0.0300310215530459</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>0.0348443665292808</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.0136161176847795</v>
+        <v>0.0299768057344485</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>0.0352318161498229</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.013866465706538</v>
+        <v>0.0299473693204419</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>0.0372151884715279</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.0150921190262917</v>
+        <v>0.0291450879664238</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>0.0378775830073374</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.0154771911641359</v>
+        <v>0.0291315042505814</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>0.0392280972977535</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.016215249962691</v>
+        <v>0.0290881351686377</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>0.0399133265404924</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.0165610243458402</v>
+        <v>0.0286103424459294</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>0.0418274197785018</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.0173884657978457</v>
+        <v>0.0282257733875349</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>0.0432150456499279</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.0178014960985234</v>
+        <v>0.0277499426045024</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>0.043887013136675</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.0179124256776226</v>
+        <v>0.0279407459203189</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>0.0450102798530241</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.0178805575281</v>
+        <v>0.0253360397456959</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>0.0456619318927602</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.017646549341684</v>
+        <v>0.023035921836221</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>0.0460365788658623</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.0173802098496583</v>
+        <v>0.0222864724611108</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>0.0461819538757145</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.0172373740977759</v>
+        <v>0.0217922014875595</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>0.046737721218998</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.0163865439719106</v>
+        <v>0.0191497243669264</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>0.0469289494403038</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.0159946495382058</v>
+        <v>0.0191156643588276</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>0.0473284825220253</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.0152849887979553</v>
+        <v>0.0196643409069829</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>0.0476176638832008</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.0149017210595589</v>
+        <v>0.0180795291539288</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>0.0477020398651993</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.0148118173784773</v>
+        <v>0.0178200732497316</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>0.0478818603254468</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.01465449248325</v>
+        <v>0.0170676612221136</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>0.0484858465787613</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.0144819813664077</v>
+        <v>0.0161597506841793</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>0.0489165459823905</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.0147031102786145</v>
+        <v>0.017485542933269</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>0.0490769583500672</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.0148580148280368</v>
+        <v>0.0182219855184802</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>0.0491873869786017</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.0149869116035904</v>
+        <v>0.0185429672201206</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>0.049236484793587</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.0150499413784169</v>
+        <v>0.0187670385329802</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>0.0500243014489914</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.0149105164404697</v>
+        <v>0.0218360883518884</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>0.0510136710889397</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.012027566139454</v>
+        <v>0.0218127934970073</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>0.0512274652043674</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>0.0123176728519489</v>
+        <v>0.0215434580247805</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>0.0519968702551478</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>0.0134941451438416</v>
+        <v>0.0209135032608254</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>0.0525879385165812</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>0.014494370351224</v>
+        <v>0.021617388771766</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>0.0526443123450929</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>0.0145926391141817</v>
+        <v>0.0217951783614422</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>0.0526443123450929</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>0.0145926391141817</v>
+        <v>0.0217951783614422</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>0.052934914111495</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.0151049440341654</v>
+        <v>0.0218340923213208</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>0.0530503233276077</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.0153106362583167</v>
+        <v>0.0214429096953148</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>0.053671526050024</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.0148961724309687</v>
+        <v>0.0223204551074106</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>0.053780373037864</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>0.0144300213259242</v>
+        <v>0.022221796194108</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>0.0551839709445726</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.0120675526169608</v>
+        <v>0.0213884776731466</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>0.0554445385696138</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>0.0125401275241475</v>
+        <v>0.0215002337887953</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>0.0563360618976567</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>0.013998326153521</v>
+        <v>0.0226654208994642</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>0.0572234227639451</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>0.0152370996301167</v>
+        <v>0.0244818912328594</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>0.0585707355765391</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>0.0198203666182993</v>
+        <v>0.0277359511406554</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>0.0596608909502932</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>0.0239698931668149</v>
+        <v>0.0278968018486457</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>0.0609649105222307</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>0.0283545045402397</v>
+        <v>0.0291217138399828</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>0.0634991629107843</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>0.0353627206879608</v>
+        <v>0.0301653001748847</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>0.0656359241528979</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>0.0399979755461378</v>
+        <v>0.0303183277590943</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>0.0691905066052672</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>0.0456841969476574</v>
+        <v>0.0304721585384843</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>0.0715270661622967</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>0.0463140703521012</v>
+        <v>0.0317904998826237</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>0.0745297331395211</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>0.046325717297755</v>
+        <v>0.0333793474409217</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>0.0761583302636734</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>0.0460930836143119</v>
+        <v>0.0341351424908175</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>0.0774525004466432</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>0.0458027741542508</v>
+        <v>0.0353366081909211</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>0.0787256144990016</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>0.0454334147149866</v>
+        <v>0.0365456003716782</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>0.0803273787749866</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>0.0448596526533101</v>
+        <v>0.0381016588287397</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>0.0817437266173278</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>0.0442586457097533</v>
+        <v>0.0398088337743646</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>0.0839843788338711</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>0.0431438148838704</v>
+        <v>0.0417687184674061</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>0.0937521562569541</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>0.0363643688535204</v>
+        <v>0.0464557325086047</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>0.0963318949439704</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>0.0341484261484301</v>
+        <v>0.0447633198999079</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>0.110664363929489</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>0.0194681889022729</v>
+        <v>0.0492093218525504</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>0.120108381478803</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>0.00854255984463517</v>
+        <v>0.0511756900484107</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>0.120979005686169</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>0.00800564628656025</v>
+        <v>0.0498760580818857</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>0.129818421008173</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>0.00302777228913697</v>
+        <v>0.0550044986310142</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>0.140076098519272</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>0.00994141421929324</v>
+        <v>0.0554383376567011</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>0.155503763416784</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>0.0320908701078606</v>
+        <v>0.0672257472741973</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>0.156162807662635</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>0.0330990985248624</v>
+        <v>0.0672559042584103</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>0.182793943792466</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>0.0733777815626325</v>
+        <v>0.105089385182292</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>0.214417557684448</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>0.0712140778049577</v>
+        <v>0.166229730937285</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>25.4972406088554</v>
+        <v>2.8136046340631</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
